--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.280076</v>
+        <v>0.559982</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,23 +453,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007429</v>
+        <v>0.030235</v>
       </c>
       <c r="C3" t="n">
-        <v>0.280076</v>
+        <v>0.559982</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mix effect</t>
+          <t>Concentration effect</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.015952</v>
+        <v>0.013573</v>
       </c>
       <c r="C4" t="n">
-        <v>0.287505</v>
+        <v>0.590217</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.303457</v>
+        <v>0.603789</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.559982</v>
+        <v>0.592711</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.030235</v>
+        <v>0.040176</v>
       </c>
       <c r="C3" t="n">
-        <v>0.559982</v>
+        <v>0.592711</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.013573</v>
+        <v>0.011277</v>
       </c>
       <c r="C4" t="n">
-        <v>0.590217</v>
+        <v>0.632887</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.603789</v>
+        <v>0.644163</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.592711</v>
+        <v>0.593262</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.040176</v>
+        <v>0.04132</v>
       </c>
       <c r="C3" t="n">
-        <v>0.592711</v>
+        <v>0.593262</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.011277</v>
+        <v>0.010686</v>
       </c>
       <c r="C4" t="n">
-        <v>0.632887</v>
+        <v>0.634582</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.644163</v>
+        <v>0.645267</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.593262</v>
+        <v>0.525852</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04132</v>
+        <v>0.035746</v>
       </c>
       <c r="C3" t="n">
-        <v>0.593262</v>
+        <v>0.525852</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.010686</v>
+        <v>0.009284000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.634582</v>
+        <v>0.561598</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.645267</v>
+        <v>0.570881</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.525852</v>
+        <v>0.526157</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.035746</v>
+        <v>0.035857</v>
       </c>
       <c r="C3" t="n">
-        <v>0.525852</v>
+        <v>0.526157</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009284000000000001</v>
+        <v>0.009148</v>
       </c>
       <c r="C4" t="n">
-        <v>0.561598</v>
+        <v>0.562014</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.570881</v>
+        <v>0.571163</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
